--- a/human_resources_forms/001_job_candidate_self_assessment--human_resources_forms.xlsx
+++ b/human_resources_forms/001_job_candidate_self_assessment--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -891,12 +891,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'0-2_years'}</t>
+          <t>0-2_years</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': '0-2 years'}</t>
+          <t>0-2 years</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'2-5_years'}</t>
+          <t>2-5_years</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '2-5 years'}</t>
+          <t>2-5 years</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'5-10_years'}</t>
+          <t>5-10_years</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '5-10 years'}</t>
+          <t>5-10 years</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'10-20_years'}</t>
+          <t>10-20_years</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '10-20 years'}</t>
+          <t>10-20 years</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_20_years'}</t>
+          <t>more_than_20_years</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'More than 20 years'}</t>
+          <t>More than 20 years</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'bsc'}</t>
+          <t>bsc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'BSc'}</t>
+          <t>BSc</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'beng'}</t>
+          <t>beng</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'BEng'}</t>
+          <t>BEng</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'bcom'}</t>
+          <t>bcom</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'BCom'}</t>
+          <t>BCom</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'ba'}</t>
+          <t>ba</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'BA'}</t>
+          <t>BA</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'bbsc'}</t>
+          <t>bbsc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'BBSc'}</t>
+          <t>BBSc</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'bba'}</t>
+          <t>bba</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'BBA'}</t>
+          <t>BBA</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'bengtech'}</t>
+          <t>bengtech</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'BEngTech'}</t>
+          <t>BEngTech</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'bmsc'}</t>
+          <t>bmsc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'BMSc'}</t>
+          <t>BMSc</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'bed'}</t>
+          <t>bed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'BEd'}</t>
+          <t>BEd</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'ma'}</t>
+          <t>ma</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'MA'}</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'mba'}</t>
+          <t>mba</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'MBA'}</t>
+          <t>MBA</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'msc'}</t>
+          <t>msc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'MSc'}</t>
+          <t>MSc</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'ph.d'}</t>
+          <t>ph.d</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Ph.D'}</t>
+          <t>Ph.D</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'mcom'}</t>
+          <t>mcom</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'MCom'}</t>
+          <t>MCom</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'meng'}</t>
+          <t>meng</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'MEng'}</t>
+          <t>MEng</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'med'}</t>
+          <t>med</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'MEd'}</t>
+          <t>MEd</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'mbsc'}</t>
+          <t>mbsc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'MBSc'}</t>
+          <t>MBSc</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'mba'}</t>
+          <t>mpeng</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'MBA'}</t>
+          <t>MPEng</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'mpeng'}</t>
+          <t>msocsc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'MPEng'}</t>
+          <t>MSocSc</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'mba'}</t>
+          <t>march</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'MBA'}</t>
+          <t>MArch</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'msocsc'}</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'MSocSc'}</t>
+          <t>PhD</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'march'}</t>
+          <t>bpeng</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'MArch'}</t>
+          <t>BPEng</t>
         </is>
       </c>
     </row>
@@ -1383,165 +1383,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'mba'}</t>
+          <t>mappl</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'MBA'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>diploma_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'label':_'bsc'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'label': 'BSc'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>diploma_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'label':_'bba'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'label': 'BBA'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>diploma_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'label':_'phd'}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'label': 'PhD'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>diploma_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'label':_'bpeng'}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'label': 'BPEng'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>diploma_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'label':_'mappl'}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'label': 'MAppl'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>diploma_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'label':_'mba'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'label': 'MBA'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>diploma_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'label':_'mba'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'label': 'MBA'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>diploma_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'label':_'mbsc'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'label': 'MBSc'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>diploma_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'label':_'mba'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'label': 'MBA'}</t>
+          <t>MAppl</t>
         </is>
       </c>
     </row>
